--- a/Ozrit HR data/ozrit/Admin/Admin payment Details/Admin Payments.xlsx
+++ b/Ozrit HR data/ozrit/Admin/Admin payment Details/Admin Payments.xlsx
@@ -8,31 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\Admin\Admin payment Details\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D92E83-59C4-4EB2-865D-BFE5F28F59CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094DC558-E64E-4945-96D4-0072701DB0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="September" sheetId="10" r:id="rId1"/>
-    <sheet name="August" sheetId="9" r:id="rId2"/>
-    <sheet name="July " sheetId="7" r:id="rId3"/>
-    <sheet name="June " sheetId="1" r:id="rId4"/>
-    <sheet name="June final " sheetId="8" r:id="rId5"/>
-    <sheet name="May" sheetId="2" r:id="rId6"/>
-    <sheet name="April" sheetId="3" r:id="rId7"/>
-    <sheet name="March" sheetId="4" r:id="rId8"/>
-    <sheet name="Feb 2025" sheetId="5" r:id="rId9"/>
-    <sheet name="Jan" sheetId="6" r:id="rId10"/>
+    <sheet name="October " sheetId="11" r:id="rId1"/>
+    <sheet name="September" sheetId="10" r:id="rId2"/>
+    <sheet name="August" sheetId="9" r:id="rId3"/>
+    <sheet name="July " sheetId="7" r:id="rId4"/>
+    <sheet name="June " sheetId="1" r:id="rId5"/>
+    <sheet name="June final " sheetId="8" r:id="rId6"/>
+    <sheet name="May" sheetId="2" r:id="rId7"/>
+    <sheet name="April" sheetId="3" r:id="rId8"/>
+    <sheet name="March" sheetId="4" r:id="rId9"/>
+    <sheet name="Feb 2025" sheetId="5" r:id="rId10"/>
+    <sheet name="Jan" sheetId="6" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">August!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">August!$A$1:$H$29</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="490">
   <si>
     <t xml:space="preserve">Date of Payments </t>
   </si>
@@ -1406,6 +1407,102 @@
   </si>
   <si>
     <t xml:space="preserve">Panthulu amount </t>
+  </si>
+  <si>
+    <t>28.10.2025</t>
+  </si>
+  <si>
+    <t>Office supplies</t>
+  </si>
+  <si>
+    <t>13.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deemart Payment </t>
+  </si>
+  <si>
+    <t>16.10,2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lapcore code </t>
+  </si>
+  <si>
+    <t xml:space="preserve">internship copies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diwali Expenses </t>
+  </si>
+  <si>
+    <t>Recharges (mahesh , ravindra, rani and mahesh)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vijay Birthday </t>
+  </si>
+  <si>
+    <t>16.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birthday HR </t>
+  </si>
+  <si>
+    <t>01.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly exp </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big rock </t>
+  </si>
+  <si>
+    <t>04.10.2025</t>
+  </si>
+  <si>
+    <t>05.10.2025</t>
+  </si>
+  <si>
+    <t>06.10.2025</t>
+  </si>
+  <si>
+    <t>07.10.2025</t>
+  </si>
+  <si>
+    <t>09.10.2025</t>
+  </si>
+  <si>
+    <t>Seo shopee</t>
+  </si>
+  <si>
+    <t>Spaceship</t>
+  </si>
+  <si>
+    <t>10.10.2025</t>
+  </si>
+  <si>
+    <t>Open Ai</t>
+  </si>
+  <si>
+    <t>17.10.2025</t>
+  </si>
+  <si>
+    <t>27.10.2025</t>
+  </si>
+  <si>
+    <t>27.10,2025</t>
+  </si>
+  <si>
+    <t>Canva</t>
+  </si>
+  <si>
+    <t>26.10.2025</t>
+  </si>
+  <si>
+    <t>28.10.205</t>
+  </si>
+  <si>
+    <t>Bigrock</t>
+  </si>
+  <si>
+    <t>29.10.2025</t>
   </si>
 </sst>
 </file>
@@ -1589,7 +1686,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1648,6 +1745,24 @@
       <patternFill patternType="solid">
         <fgColor theme="2"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1958,7 +2073,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2197,6 +2312,28 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2224,7 +2361,12 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2439,337 +2581,511 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F52BF488-E69E-4573-83FE-2A66BD0987F9}">
-  <dimension ref="A1:K18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7736012D-9FC2-42BE-AB17-18C767AD98B4}">
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" customWidth="1"/>
     <col min="4" max="4" width="44.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" customWidth="1"/>
-    <col min="6" max="6" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="119" t="s">
+    <row r="1" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119" t="s">
+      <c r="B1" s="130"/>
+      <c r="C1" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="119" t="s">
+      <c r="D1" s="130" t="s">
         <v>432</v>
       </c>
-      <c r="E1" s="119" t="s">
+      <c r="E1" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="120" t="s">
+      <c r="F1" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="49"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
-        <v>426</v>
-      </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49" t="s">
-        <v>424</v>
-      </c>
-      <c r="D2" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="E2" s="49">
+      <c r="G1" s="132"/>
+    </row>
+    <row r="2" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="147" t="s">
+        <v>470</v>
+      </c>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E2" s="147">
+        <v>2297.46</v>
+      </c>
+      <c r="F2" s="148"/>
+      <c r="G2" s="149"/>
+    </row>
+    <row r="3" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="147" t="s">
+        <v>473</v>
+      </c>
+      <c r="B3" s="147"/>
+      <c r="C3" s="147" t="s">
+        <v>472</v>
+      </c>
+      <c r="D3" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E3" s="147">
+        <v>978.22</v>
+      </c>
+      <c r="F3" s="148"/>
+      <c r="G3" s="149"/>
+    </row>
+    <row r="4" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="147" t="s">
+        <v>474</v>
+      </c>
+      <c r="B4" s="147"/>
+      <c r="C4" s="147" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E4" s="147">
+        <v>341.02</v>
+      </c>
+      <c r="F4" s="148"/>
+      <c r="G4" s="149"/>
+    </row>
+    <row r="5" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="147" t="s">
+        <v>475</v>
+      </c>
+      <c r="B5" s="147"/>
+      <c r="C5" s="147" t="s">
+        <v>443</v>
+      </c>
+      <c r="D5" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E5" s="147">
+        <v>2953.32</v>
+      </c>
+      <c r="F5" s="148"/>
+      <c r="G5" s="149"/>
+    </row>
+    <row r="6" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="147" t="s">
+        <v>476</v>
+      </c>
+      <c r="B6" s="147"/>
+      <c r="C6" s="147" t="s">
+        <v>443</v>
+      </c>
+      <c r="D6" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E6" s="147">
+        <v>1001.82</v>
+      </c>
+      <c r="F6" s="148"/>
+      <c r="G6" s="149"/>
+    </row>
+    <row r="7" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="147" t="s">
+        <v>477</v>
+      </c>
+      <c r="B7" s="147"/>
+      <c r="C7" s="147" t="s">
+        <v>478</v>
+      </c>
+      <c r="D7" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E7" s="147">
+        <v>549</v>
+      </c>
+      <c r="F7" s="148"/>
+      <c r="G7" s="149"/>
+    </row>
+    <row r="8" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="147" t="s">
+        <v>477</v>
+      </c>
+      <c r="B8" s="147"/>
+      <c r="C8" s="147" t="s">
+        <v>479</v>
+      </c>
+      <c r="D8" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E8" s="147">
+        <v>796</v>
+      </c>
+      <c r="F8" s="148"/>
+      <c r="G8" s="149"/>
+    </row>
+    <row r="9" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="147" t="s">
+        <v>480</v>
+      </c>
+      <c r="B9" s="147"/>
+      <c r="C9" s="147" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E9" s="147">
+        <v>409.22</v>
+      </c>
+      <c r="F9" s="148"/>
+      <c r="G9" s="149"/>
+    </row>
+    <row r="10" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="147" t="s">
+        <v>460</v>
+      </c>
+      <c r="B10" s="147"/>
+      <c r="C10" s="147" t="s">
+        <v>443</v>
+      </c>
+      <c r="D10" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E10" s="147">
+        <v>1758.2</v>
+      </c>
+      <c r="F10" s="148"/>
+      <c r="G10" s="149"/>
+    </row>
+    <row r="11" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="147" t="s">
+        <v>460</v>
+      </c>
+      <c r="B11" s="147"/>
+      <c r="C11" s="147" t="s">
+        <v>481</v>
+      </c>
+      <c r="D11" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E11" s="147">
+        <v>399</v>
+      </c>
+      <c r="F11" s="148"/>
+      <c r="G11" s="149"/>
+    </row>
+    <row r="12" spans="1:8" s="129" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="133" t="s">
+        <v>460</v>
+      </c>
+      <c r="B12" s="133"/>
+      <c r="C12" s="133" t="s">
+        <v>459</v>
+      </c>
+      <c r="D12" s="133" t="s">
+        <v>461</v>
+      </c>
+      <c r="E12" s="133">
+        <v>3441</v>
+      </c>
+      <c r="F12" s="133"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+    </row>
+    <row r="13" spans="1:8" s="129" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="133" t="s">
+        <v>468</v>
+      </c>
+      <c r="B13" s="133"/>
+      <c r="C13" s="133" t="s">
+        <v>459</v>
+      </c>
+      <c r="D13" s="133" t="s">
+        <v>469</v>
+      </c>
+      <c r="E13" s="133">
+        <v>800</v>
+      </c>
+      <c r="F13" s="133"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+    </row>
+    <row r="14" spans="1:8" s="129" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="133" t="s">
+        <v>462</v>
+      </c>
+      <c r="B14" s="133"/>
+      <c r="C14" s="133" t="s">
+        <v>459</v>
+      </c>
+      <c r="D14" s="133" t="s">
+        <v>463</v>
+      </c>
+      <c r="E14" s="134">
+        <v>1800</v>
+      </c>
+      <c r="F14" s="133"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
+    </row>
+    <row r="15" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="147" t="s">
+        <v>468</v>
+      </c>
+      <c r="B15" s="147"/>
+      <c r="C15" s="147" t="s">
+        <v>479</v>
+      </c>
+      <c r="D15" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E15" s="147">
+        <v>796</v>
+      </c>
+      <c r="F15" s="148"/>
+      <c r="G15" s="149"/>
+    </row>
+    <row r="16" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="147" t="s">
+        <v>482</v>
+      </c>
+      <c r="B16" s="147"/>
+      <c r="C16" s="147" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E16" s="147">
+        <v>2728.16</v>
+      </c>
+      <c r="F16" s="148"/>
+      <c r="G16" s="149"/>
+    </row>
+    <row r="17" spans="1:8" s="129" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="133" t="s">
+        <v>486</v>
+      </c>
+      <c r="B17" s="133"/>
+      <c r="C17" s="133" t="s">
+        <v>485</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>471</v>
+      </c>
+      <c r="E17" s="134">
+        <v>500</v>
+      </c>
+      <c r="F17" s="133"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+    </row>
+    <row r="18" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="147" t="s">
+        <v>483</v>
+      </c>
+      <c r="B18" s="147"/>
+      <c r="C18" s="147" t="s">
+        <v>443</v>
+      </c>
+      <c r="D18" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E18" s="147">
+        <v>942.82</v>
+      </c>
+      <c r="F18" s="148"/>
+      <c r="G18" s="149"/>
+    </row>
+    <row r="19" spans="1:8" s="150" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="147" t="s">
+        <v>484</v>
+      </c>
+      <c r="B19" s="147"/>
+      <c r="C19" s="147" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="147" t="s">
+        <v>471</v>
+      </c>
+      <c r="E19" s="147">
+        <v>2728.16</v>
+      </c>
+      <c r="F19" s="148"/>
+      <c r="G19" s="149"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="136" t="s">
+        <v>458</v>
+      </c>
+      <c r="B20" s="137"/>
+      <c r="C20" s="136" t="s">
+        <v>459</v>
+      </c>
+      <c r="D20" s="136" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="137">
+        <v>5600</v>
+      </c>
+      <c r="F20" s="137"/>
+      <c r="G20" s="137"/>
+      <c r="H20" s="137"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="136" t="s">
+        <v>458</v>
+      </c>
+      <c r="B21" s="137"/>
+      <c r="C21" s="136" t="s">
+        <v>459</v>
+      </c>
+      <c r="D21" s="136" t="s">
+        <v>464</v>
+      </c>
+      <c r="E21" s="137">
+        <v>496</v>
+      </c>
+      <c r="F21" s="137"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="137"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="136" t="s">
+        <v>458</v>
+      </c>
+      <c r="B22" s="137"/>
+      <c r="C22" s="136" t="s">
+        <v>459</v>
+      </c>
+      <c r="D22" s="136" t="s">
+        <v>465</v>
+      </c>
+      <c r="E22" s="137">
+        <v>5804</v>
+      </c>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="137"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="136" t="s">
+        <v>458</v>
+      </c>
+      <c r="B23" s="137"/>
+      <c r="C23" s="136" t="s">
+        <v>459</v>
+      </c>
+      <c r="D23" s="136" t="s">
+        <v>466</v>
+      </c>
+      <c r="E23" s="137">
+        <v>892</v>
+      </c>
+      <c r="F23" s="137"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="137"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="136" t="s">
+        <v>458</v>
+      </c>
+      <c r="B24" s="137"/>
+      <c r="C24" s="136" t="s">
+        <v>459</v>
+      </c>
+      <c r="D24" s="136" t="s">
+        <v>467</v>
+      </c>
+      <c r="E24" s="137">
+        <v>850</v>
+      </c>
+      <c r="F24" s="137"/>
+      <c r="G24" s="137"/>
+      <c r="H24" s="137"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="137" t="s">
+        <v>487</v>
+      </c>
+      <c r="B25" s="137"/>
+      <c r="C25" s="137" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="137" t="s">
+        <v>471</v>
+      </c>
+      <c r="E25" s="137">
+        <v>1344.02</v>
+      </c>
+      <c r="F25" s="137"/>
+      <c r="G25" s="137"/>
+      <c r="H25" s="137"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="137" t="s">
+        <v>489</v>
+      </c>
+      <c r="B26" s="137"/>
+      <c r="C26" s="137" t="s">
+        <v>488</v>
+      </c>
+      <c r="D26" s="137" t="s">
+        <v>471</v>
+      </c>
+      <c r="E26" s="137">
         <v>848.42</v>
       </c>
-      <c r="F2" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="49"/>
-      <c r="K2" s="66" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
-        <v>427</v>
-      </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="E3" s="49">
-        <v>1650.82</v>
-      </c>
-      <c r="F3" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="49"/>
-      <c r="K3" s="66" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="49" t="s">
-        <v>437</v>
-      </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49" t="s">
-        <v>438</v>
-      </c>
-      <c r="D4" s="50"/>
-      <c r="E4" s="49">
-        <v>549</v>
-      </c>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="K4" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
-        <v>439</v>
-      </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="49">
-        <v>409.22</v>
-      </c>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="K5" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
-        <v>436</v>
-      </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="49">
-        <v>3766</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="49"/>
-      <c r="K6" s="66" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
-        <v>440</v>
-      </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49" t="s">
-        <v>441</v>
-      </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="122">
-        <v>3710.26</v>
-      </c>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="K7" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="50" t="s">
-        <v>440</v>
-      </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50" t="s">
-        <v>441</v>
-      </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49">
-        <v>800</v>
-      </c>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="K8" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="50" t="s">
-        <v>442</v>
-      </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="50" t="s">
-        <v>443</v>
-      </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49">
-        <v>1758.2</v>
-      </c>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="K9" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="50" t="s">
-        <v>442</v>
-      </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="50" t="s">
-        <v>443</v>
-      </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49">
-        <v>1049.0999999999999</v>
-      </c>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="K10" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
-        <v>455</v>
-      </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50" t="s">
-        <v>454</v>
-      </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49">
-        <v>1709</v>
-      </c>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-    </row>
-    <row r="12" spans="1:11" ht="13" x14ac:dyDescent="0.3">
-      <c r="A12" s="50" t="s">
-        <v>455</v>
-      </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49">
-        <v>1230</v>
-      </c>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="K12" s="63" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="50" t="s">
-        <v>455</v>
-      </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50" t="s">
-        <v>456</v>
-      </c>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49">
-        <v>5280</v>
-      </c>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
-        <v>455</v>
-      </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="50" t="s">
-        <v>457</v>
-      </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49">
-        <v>1167</v>
-      </c>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="49"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="137" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="127">
-        <f>SUM(E2:E14)</f>
-        <v>23927.020000000004</v>
-      </c>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="49"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="49"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="49"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
+      <c r="F26" s="137"/>
+      <c r="G26" s="137"/>
+      <c r="H26" s="137"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="137" t="s">
+        <v>489</v>
+      </c>
+      <c r="B27" s="137"/>
+      <c r="C27" s="137" t="s">
+        <v>488</v>
+      </c>
+      <c r="D27" s="137" t="s">
+        <v>471</v>
+      </c>
+      <c r="E27" s="137">
+        <v>848.42</v>
+      </c>
+      <c r="F27" s="137"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="137"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Mis exp" prompt="Mis exp" sqref="D3:D5" xr:uid="{22B07D60-22AD-45E9-9C2F-CF4D875F57FB}"/>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" customWidth="1"/>
+    <col min="3" max="3" width="34.08984375" customWidth="1"/>
     <col min="4" max="4" width="25.7265625" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>57</v>
+      <c r="A1" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -2807,6 +3123,152 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="36">
+        <v>45689</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" s="5">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="36">
+        <v>45693</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E3" s="5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E4" s="5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>353</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5">
+        <v>8182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="37">
+        <v>45711</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="E6" s="38">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D7" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="40">
+        <f>SUM(E2:E6)</f>
+        <v>11172</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:Z21"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.36328125" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="25.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+    </row>
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="36">
         <v>45675</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -2969,6 +3431,324 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F52BF488-E69E-4573-83FE-2A66BD0987F9}">
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" customWidth="1"/>
+    <col min="6" max="6" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="119" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="119" t="s">
+        <v>432</v>
+      </c>
+      <c r="E1" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="120" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="49"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="49" t="s">
+        <v>426</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="49">
+        <v>848.42</v>
+      </c>
+      <c r="F2" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="49"/>
+      <c r="K2" s="66" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
+        <v>427</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="49">
+        <v>1650.82</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="49"/>
+      <c r="K3" s="66" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="49" t="s">
+        <v>437</v>
+      </c>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49" t="s">
+        <v>438</v>
+      </c>
+      <c r="D4" s="50"/>
+      <c r="E4" s="49">
+        <v>549</v>
+      </c>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="K4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="49" t="s">
+        <v>439</v>
+      </c>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="50"/>
+      <c r="E5" s="49">
+        <v>409.22</v>
+      </c>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="K5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="49" t="s">
+        <v>436</v>
+      </c>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="50"/>
+      <c r="E6" s="49">
+        <v>3766</v>
+      </c>
+      <c r="F6" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="49"/>
+      <c r="K6" s="66" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="49" t="s">
+        <v>440</v>
+      </c>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49" t="s">
+        <v>441</v>
+      </c>
+      <c r="D7" s="50"/>
+      <c r="E7" s="122">
+        <v>3710.26</v>
+      </c>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="K7" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="50" t="s">
+        <v>440</v>
+      </c>
+      <c r="B8" s="49"/>
+      <c r="C8" s="50" t="s">
+        <v>441</v>
+      </c>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49">
+        <v>800</v>
+      </c>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="K8" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="50" t="s">
+        <v>442</v>
+      </c>
+      <c r="B9" s="49"/>
+      <c r="C9" s="50" t="s">
+        <v>443</v>
+      </c>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49">
+        <v>1758.2</v>
+      </c>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="K9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="50" t="s">
+        <v>442</v>
+      </c>
+      <c r="B10" s="49"/>
+      <c r="C10" s="50" t="s">
+        <v>443</v>
+      </c>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49">
+        <v>1049.0999999999999</v>
+      </c>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="K10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="50" t="s">
+        <v>455</v>
+      </c>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50" t="s">
+        <v>454</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49">
+        <v>1709</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>451</v>
+      </c>
+      <c r="G11" s="49"/>
+    </row>
+    <row r="12" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+      <c r="A12" s="50" t="s">
+        <v>455</v>
+      </c>
+      <c r="B12" s="49"/>
+      <c r="C12" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49">
+        <v>1230</v>
+      </c>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="K12" s="63" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="50" t="s">
+        <v>455</v>
+      </c>
+      <c r="B13" s="49"/>
+      <c r="C13" s="50" t="s">
+        <v>456</v>
+      </c>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49">
+        <v>5280</v>
+      </c>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="50" t="s">
+        <v>455</v>
+      </c>
+      <c r="B14" s="49"/>
+      <c r="C14" s="50" t="s">
+        <v>457</v>
+      </c>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49">
+        <v>1167</v>
+      </c>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="49"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="128" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="127">
+        <f>SUM(E2:E14)</f>
+        <v>23927.020000000004</v>
+      </c>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="49"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="49"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="49"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Mis exp" prompt="Mis exp" sqref="D3:D5" xr:uid="{22B07D60-22AD-45E9-9C2F-CF4D875F57FB}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J30"/>
@@ -3580,7 +4360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z62"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -3685,7 +4465,7 @@
       <c r="I3" t="s">
         <v>266</v>
       </c>
-      <c r="N3" s="130" t="s">
+      <c r="N3" s="140" t="s">
         <v>382</v>
       </c>
       <c r="O3" s="49" t="s">
@@ -3714,7 +4494,7 @@
       <c r="I4" t="s">
         <v>267</v>
       </c>
-      <c r="N4" s="131"/>
+      <c r="N4" s="141"/>
       <c r="O4" s="49" t="s">
         <v>289</v>
       </c>
@@ -3741,7 +4521,7 @@
       <c r="I5">
         <v>1139</v>
       </c>
-      <c r="N5" s="131"/>
+      <c r="N5" s="141"/>
       <c r="O5" s="49" t="s">
         <v>320</v>
       </c>
@@ -3765,7 +4545,7 @@
       <c r="F6" s="49" t="s">
         <v>287</v>
       </c>
-      <c r="N6" s="131"/>
+      <c r="N6" s="141"/>
       <c r="O6" s="49" t="s">
         <v>319</v>
       </c>
@@ -3787,7 +4567,7 @@
         <v>790</v>
       </c>
       <c r="F7" s="49"/>
-      <c r="N7" s="131"/>
+      <c r="N7" s="141"/>
       <c r="O7" s="49" t="s">
         <v>324</v>
       </c>
@@ -3811,7 +4591,7 @@
       <c r="F8" s="49" t="s">
         <v>294</v>
       </c>
-      <c r="N8" s="131"/>
+      <c r="N8" s="141"/>
       <c r="O8" s="50" t="s">
         <v>337</v>
       </c>
@@ -3841,7 +4621,7 @@
       <c r="K9" t="s">
         <v>295</v>
       </c>
-      <c r="N9" s="131"/>
+      <c r="N9" s="141"/>
       <c r="O9" s="50" t="s">
         <v>339</v>
       </c>
@@ -3865,7 +4645,7 @@
       <c r="F10" s="49" t="s">
         <v>293</v>
       </c>
-      <c r="N10" s="131"/>
+      <c r="N10" s="141"/>
       <c r="O10" s="50" t="s">
         <v>342</v>
       </c>
@@ -3889,7 +4669,7 @@
       <c r="F11" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="N11" s="131"/>
+      <c r="N11" s="141"/>
       <c r="O11" s="50" t="s">
         <v>347</v>
       </c>
@@ -3913,7 +4693,7 @@
       <c r="F12" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="N12" s="131"/>
+      <c r="N12" s="141"/>
       <c r="O12" s="50" t="s">
         <v>363</v>
       </c>
@@ -3940,7 +4720,7 @@
       <c r="G13" t="s">
         <v>322</v>
       </c>
-      <c r="N13" s="131"/>
+      <c r="N13" s="141"/>
       <c r="O13" s="50" t="s">
         <v>362</v>
       </c>
@@ -3976,7 +4756,7 @@
       <c r="L14" s="103" t="s">
         <v>375</v>
       </c>
-      <c r="N14" s="132"/>
+      <c r="N14" s="142"/>
       <c r="O14" s="50" t="s">
         <v>55</v>
       </c>
@@ -4006,7 +4786,7 @@
       <c r="L15" s="62">
         <v>1400</v>
       </c>
-      <c r="N15" s="132"/>
+      <c r="N15" s="142"/>
       <c r="O15" s="49" t="s">
         <v>298</v>
       </c>
@@ -4032,7 +4812,7 @@
         <v>35</v>
       </c>
       <c r="G16" s="91"/>
-      <c r="J16" s="128" t="s">
+      <c r="J16" s="138" t="s">
         <v>376</v>
       </c>
       <c r="K16" s="104" t="s">
@@ -4041,7 +4821,7 @@
       <c r="L16" s="105">
         <v>5112</v>
       </c>
-      <c r="N16" s="132"/>
+      <c r="N16" s="142"/>
       <c r="O16" s="49" t="s">
         <v>299</v>
       </c>
@@ -4065,14 +4845,14 @@
         <v>29</v>
       </c>
       <c r="G17" s="91"/>
-      <c r="J17" s="129"/>
+      <c r="J17" s="139"/>
       <c r="K17" s="104" t="s">
         <v>145</v>
       </c>
       <c r="L17" s="105">
         <v>4743</v>
       </c>
-      <c r="N17" s="132"/>
+      <c r="N17" s="142"/>
       <c r="O17" s="49" t="s">
         <v>317</v>
       </c>
@@ -4096,14 +4876,14 @@
         <v>29</v>
       </c>
       <c r="G18" s="91"/>
-      <c r="J18" s="129"/>
+      <c r="J18" s="139"/>
       <c r="K18" s="104" t="s">
         <v>378</v>
       </c>
       <c r="L18" s="105">
         <v>300</v>
       </c>
-      <c r="N18" s="132"/>
+      <c r="N18" s="142"/>
       <c r="O18" s="49" t="s">
         <v>318</v>
       </c>
@@ -4127,14 +4907,14 @@
         <v>29</v>
       </c>
       <c r="G19" s="91"/>
-      <c r="J19" s="129"/>
+      <c r="J19" s="139"/>
       <c r="K19" s="104" t="s">
         <v>87</v>
       </c>
       <c r="L19" s="105">
         <v>3710</v>
       </c>
-      <c r="N19" s="132"/>
+      <c r="N19" s="142"/>
       <c r="O19" s="49" t="s">
         <v>298</v>
       </c>
@@ -4158,14 +4938,14 @@
         <v>29</v>
       </c>
       <c r="G20" s="91"/>
-      <c r="J20" s="129"/>
+      <c r="J20" s="139"/>
       <c r="K20" s="104" t="s">
         <v>195</v>
       </c>
       <c r="L20" s="105">
         <v>270</v>
       </c>
-      <c r="N20" s="132"/>
+      <c r="N20" s="142"/>
       <c r="O20" s="115" t="s">
         <v>430</v>
       </c>
@@ -4189,14 +4969,14 @@
         <v>29</v>
       </c>
       <c r="G21" s="91"/>
-      <c r="J21" s="129"/>
+      <c r="J21" s="139"/>
       <c r="K21" s="104" t="s">
         <v>379</v>
       </c>
       <c r="L21" s="105">
         <v>647</v>
       </c>
-      <c r="N21" s="132"/>
+      <c r="N21" s="142"/>
       <c r="O21" s="115"/>
       <c r="P21" s="117">
         <f>SUM(P3:P20)</f>
@@ -4222,14 +5002,14 @@
         <v>29</v>
       </c>
       <c r="G22" s="91"/>
-      <c r="J22" s="129"/>
+      <c r="J22" s="139"/>
       <c r="K22" s="104" t="s">
         <v>304</v>
       </c>
       <c r="L22" s="105">
         <v>500</v>
       </c>
-      <c r="N22" s="132"/>
+      <c r="N22" s="142"/>
       <c r="O22" s="115"/>
       <c r="P22" s="116">
         <v>-33</v>
@@ -4251,14 +5031,14 @@
         <v>29</v>
       </c>
       <c r="G23" s="91"/>
-      <c r="J23" s="129"/>
+      <c r="J23" s="139"/>
       <c r="K23" s="104" t="s">
         <v>17</v>
       </c>
       <c r="L23" s="105">
         <v>7079</v>
       </c>
-      <c r="N23" s="132"/>
+      <c r="N23" s="142"/>
       <c r="O23" s="115"/>
       <c r="P23" s="115"/>
     </row>
@@ -4281,7 +5061,7 @@
       <c r="H24" t="s">
         <v>390</v>
       </c>
-      <c r="J24" s="129"/>
+      <c r="J24" s="139"/>
       <c r="K24" s="110" t="s">
         <v>56</v>
       </c>
@@ -4289,7 +5069,7 @@
         <f>SUM(L15:L23)</f>
         <v>23761</v>
       </c>
-      <c r="N24" s="131"/>
+      <c r="N24" s="141"/>
       <c r="O24" s="114"/>
       <c r="P24" s="114"/>
     </row>
@@ -4312,7 +5092,7 @@
       <c r="H25" t="s">
         <v>391</v>
       </c>
-      <c r="J25" s="134" t="s">
+      <c r="J25" s="144" t="s">
         <v>380</v>
       </c>
       <c r="K25" s="50" t="s">
@@ -4321,7 +5101,7 @@
       <c r="L25" s="97">
         <v>45000</v>
       </c>
-      <c r="N25" s="131"/>
+      <c r="N25" s="141"/>
       <c r="O25" s="105"/>
       <c r="P25" s="105"/>
     </row>
@@ -4344,14 +5124,14 @@
       <c r="H26" t="s">
         <v>392</v>
       </c>
-      <c r="J26" s="135"/>
+      <c r="J26" s="145"/>
       <c r="K26" s="50" t="s">
         <v>327</v>
       </c>
       <c r="L26" s="97">
         <v>27000</v>
       </c>
-      <c r="N26" s="131"/>
+      <c r="N26" s="141"/>
       <c r="O26" s="105"/>
       <c r="P26" s="105"/>
     </row>
@@ -4374,14 +5154,14 @@
       <c r="H27" s="62">
         <v>3298</v>
       </c>
-      <c r="J27" s="135"/>
+      <c r="J27" s="145"/>
       <c r="K27" s="49" t="s">
         <v>242</v>
       </c>
       <c r="L27" s="97">
         <v>15000</v>
       </c>
-      <c r="N27" s="131"/>
+      <c r="N27" s="141"/>
       <c r="O27" s="105"/>
       <c r="P27" s="105"/>
     </row>
@@ -4401,14 +5181,14 @@
         <v>29</v>
       </c>
       <c r="G28" s="91"/>
-      <c r="J28" s="135"/>
+      <c r="J28" s="145"/>
       <c r="K28" s="50" t="s">
         <v>348</v>
       </c>
       <c r="L28" s="97">
         <v>6000</v>
       </c>
-      <c r="N28" s="131"/>
+      <c r="N28" s="141"/>
       <c r="O28" s="105"/>
       <c r="P28" s="105"/>
     </row>
@@ -4430,14 +5210,14 @@
       <c r="G29" s="91" t="s">
         <v>360</v>
       </c>
-      <c r="J29" s="135"/>
+      <c r="J29" s="145"/>
       <c r="K29" s="50" t="s">
         <v>371</v>
       </c>
       <c r="L29" s="98">
         <v>1490</v>
       </c>
-      <c r="N29" s="131"/>
+      <c r="N29" s="141"/>
       <c r="O29" s="105"/>
       <c r="P29" s="105"/>
     </row>
@@ -4457,14 +5237,14 @@
         <v>29</v>
       </c>
       <c r="G30" s="91"/>
-      <c r="J30" s="135"/>
+      <c r="J30" s="145"/>
       <c r="K30" s="49" t="s">
         <v>291</v>
       </c>
       <c r="L30" s="98">
         <v>220</v>
       </c>
-      <c r="N30" s="131"/>
+      <c r="N30" s="141"/>
       <c r="O30" s="105"/>
       <c r="P30" s="105"/>
     </row>
@@ -4484,14 +5264,14 @@
         <v>29</v>
       </c>
       <c r="G31" s="91"/>
-      <c r="J31" s="135"/>
+      <c r="J31" s="145"/>
       <c r="K31" s="50" t="s">
         <v>341</v>
       </c>
       <c r="L31" s="101">
         <v>7417</v>
       </c>
-      <c r="N31" s="131"/>
+      <c r="N31" s="141"/>
       <c r="O31" s="105"/>
       <c r="P31" s="105"/>
     </row>
@@ -4511,14 +5291,14 @@
         <v>29</v>
       </c>
       <c r="G32" s="91"/>
-      <c r="J32" s="135"/>
+      <c r="J32" s="145"/>
       <c r="K32" s="112" t="s">
         <v>383</v>
       </c>
       <c r="L32" s="101">
         <v>14500</v>
       </c>
-      <c r="N32" s="131"/>
+      <c r="N32" s="141"/>
       <c r="O32" s="105"/>
       <c r="P32" s="105"/>
     </row>
@@ -4536,14 +5316,14 @@
         <v>369</v>
       </c>
       <c r="G33" s="91"/>
-      <c r="J33" s="135"/>
+      <c r="J33" s="145"/>
       <c r="K33" s="112" t="s">
         <v>384</v>
       </c>
       <c r="L33" s="101">
         <v>5000</v>
       </c>
-      <c r="N33" s="131"/>
+      <c r="N33" s="141"/>
       <c r="O33" s="105"/>
       <c r="P33" s="105"/>
     </row>
@@ -4557,14 +5337,14 @@
         <v>181591.79</v>
       </c>
       <c r="F34" s="49"/>
-      <c r="J34" s="135"/>
+      <c r="J34" s="145"/>
       <c r="K34" s="112" t="s">
         <v>385</v>
       </c>
       <c r="L34" s="101">
         <v>1000</v>
       </c>
-      <c r="N34" s="131"/>
+      <c r="N34" s="141"/>
       <c r="O34" s="105"/>
       <c r="P34" s="105"/>
     </row>
@@ -4575,14 +5355,14 @@
       <c r="D35" s="107"/>
       <c r="E35" s="108"/>
       <c r="F35" s="107"/>
-      <c r="J35" s="136"/>
+      <c r="J35" s="146"/>
       <c r="K35" s="112" t="s">
         <v>387</v>
       </c>
       <c r="L35" s="101">
         <v>3000</v>
       </c>
-      <c r="N35" s="131"/>
+      <c r="N35" s="141"/>
       <c r="O35" s="105"/>
       <c r="P35" s="105"/>
     </row>
@@ -4597,7 +5377,7 @@
       <c r="L36" s="109">
         <v>125627</v>
       </c>
-      <c r="N36" s="131"/>
+      <c r="N36" s="141"/>
       <c r="O36" s="105"/>
       <c r="P36" s="105"/>
     </row>
@@ -4609,7 +5389,7 @@
       <c r="E37" s="108"/>
       <c r="F37" s="107"/>
       <c r="L37" s="62"/>
-      <c r="N37" s="131"/>
+      <c r="N37" s="141"/>
       <c r="O37" s="105"/>
       <c r="P37" s="105"/>
     </row>
@@ -4624,7 +5404,7 @@
       <c r="F38" s="107"/>
       <c r="K38" s="88"/>
       <c r="L38" s="62"/>
-      <c r="N38" s="131"/>
+      <c r="N38" s="141"/>
       <c r="O38" s="105"/>
       <c r="P38" s="105"/>
     </row>
@@ -4641,7 +5421,7 @@
       <c r="M39" t="s">
         <v>176</v>
       </c>
-      <c r="N39" s="131"/>
+      <c r="N39" s="141"/>
       <c r="O39" s="105"/>
       <c r="P39" s="105"/>
     </row>
@@ -4658,7 +5438,7 @@
       <c r="M40" t="s">
         <v>44</v>
       </c>
-      <c r="N40" s="131"/>
+      <c r="N40" s="141"/>
       <c r="O40" s="105"/>
       <c r="P40" s="105"/>
     </row>
@@ -4675,7 +5455,7 @@
       <c r="M41" t="s">
         <v>44</v>
       </c>
-      <c r="N41" s="131"/>
+      <c r="N41" s="141"/>
       <c r="O41" s="105"/>
       <c r="P41" s="105"/>
     </row>
@@ -4689,7 +5469,7 @@
       <c r="L42" t="s">
         <v>301</v>
       </c>
-      <c r="N42" s="131"/>
+      <c r="N42" s="141"/>
       <c r="O42" s="105"/>
       <c r="P42" s="105"/>
     </row>
@@ -4706,7 +5486,7 @@
       <c r="M43" t="s">
         <v>48</v>
       </c>
-      <c r="N43" s="133"/>
+      <c r="N43" s="143"/>
       <c r="O43" s="106" t="s">
         <v>56</v>
       </c>
@@ -4910,7 +5690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8804,7 +9584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z58"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -9953,7 +10733,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -13550,7 +14330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -13919,7 +14699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -18252,152 +19032,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:Z7"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.36328125" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" customWidth="1"/>
-    <col min="3" max="3" width="34.08984375" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-    </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36">
-        <v>45689</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E2" s="5">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36">
-        <v>45693</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E3" s="5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E4" s="5">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>353</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5">
-        <v>8182</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37">
-        <v>45711</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="E6" s="38">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D7" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="40">
-        <f>SUM(E2:E6)</f>
-        <v>11172</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>